--- a/old/260718.xlsx
+++ b/old/260718.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52293778-25CF-465C-A3CE-4B336583D2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DD95C7-6FFC-4A73-9F45-E9631DA11AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7020" yWindow="4190" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8470" yWindow="2810" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>ein geordnetes Wagnis erscheinen lassen, dort zu investieren.
 Und deshalb wundert mich die Debatte nicht – sie muss geführt werden.
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>zusammengebrochen</t>
-  </si>
-  <si>
-    <t>Jetzt schauen wir mal rein auf</t>
   </si>
   <si>
     <t>Zeitplan</t>
@@ -449,7 +446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61289ED6-4026-4582-8582-D01CC58924EC}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.5" customWidth="1"/>
@@ -468,11 +465,6 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
